--- a/_downloads/109b9f5d55724f74347a38b45829e0da/Ejemplo distribución triangular.xlsx
+++ b/_downloads/109b9f5d55724f74347a38b45829e0da/Ejemplo distribución triangular.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Dropbox\ITM\ANÁLISIS DE RIESGOS\Archivos de Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F2C40F-9AEA-4C88-9CAB-2BDFE591C075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9902A52C-208A-463F-BF0A-6897A5F9E3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{104F5D76-1E87-47BA-AC26-E17CBF973BB8}"/>
   </bookViews>
@@ -69,7 +69,7 @@
     <t>Aleatorio</t>
   </si>
   <si>
-    <t>&gt;=SI(B11&lt;=($C$7-$C$6)/($C$8-$C$6);$C$6+RAIZ(B11*$C$7*($C$8-$C$6));$C$8+RAIZ((1-B11)*($C$7-$C$6)*($C$8-$C$6)))</t>
+    <t>&gt;=SI(B10&lt;=($C$6-$C$5)/($C$7-$C$5);$C$5+RAIZ(B10*($C$6-$C$5)*($C$7-$C$5));$C$7-RAIZ((1-B10)*($C$6-$C$5)*($C$7-$C$5)))</t>
   </si>
 </sst>
 </file>
@@ -184,17 +184,17 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1099705</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>151534</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>756805</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>92716</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>6125</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CuadroTexto 12">
@@ -208,8 +208,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3506932" y="627784"/>
-              <a:ext cx="3055793" cy="300534"/>
+              <a:off x="3506932" y="549852"/>
+              <a:ext cx="3055793" cy="291875"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -365,13 +365,31 @@
                         <a:rPr lang="es-MX" sz="900" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
+                        <m:t>(</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
                         <m:t>𝑏</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="es-MX" sz="900" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
-                        <m:t>(</m:t>
+                        <m:t>−</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝑎</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>)(</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="es-MX" sz="900" b="0" i="1">
@@ -494,7 +512,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CuadroTexto 12">
@@ -508,8 +526,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3506932" y="627784"/>
-              <a:ext cx="3055793" cy="300534"/>
+              <a:off x="3506932" y="549852"/>
+              <a:ext cx="3055793" cy="291875"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -629,7 +647,7 @@
                 <a:rPr lang="es-MX" sz="900" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑃(&lt;𝑥)𝑏(𝑐−𝑎))</a:t>
+                <a:t>𝑃(&lt;𝑥)(𝑏−𝑎)(𝑐−𝑎))</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-CO" sz="900"/>
@@ -658,19 +676,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>17319</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>127579</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1026101</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>6351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>512619</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>133704</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>562840</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>12476</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CuadroTexto 13">
@@ -684,8 +702,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3537239" y="963181"/>
-              <a:ext cx="2781300" cy="291875"/>
+              <a:off x="3433328" y="841953"/>
+              <a:ext cx="3697432" cy="291875"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -793,10 +811,25 @@
             <a:p>
               <a:r>
                 <a:rPr lang="es-MX" sz="900"/>
-                <a:t>x = c + </a:t>
+                <a:t>x = </a:t>
               </a:r>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:r>
+                    <m:rPr>
+                      <m:sty m:val="p"/>
+                    </m:rPr>
+                    <a:rPr lang="es-MX" sz="900" b="0" i="0">
+                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    </a:rPr>
+                    <m:t>c</m:t>
+                  </m:r>
+                  <m:r>
+                    <a:rPr lang="es-MX" sz="900" b="0" i="0">
+                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    </a:rPr>
+                    <m:t>−</m:t>
+                  </m:r>
                   <m:rad>
                     <m:radPr>
                       <m:degHide m:val="on"/>
@@ -903,7 +936,15 @@
               </a14:m>
               <a:r>
                 <a:rPr lang="es-CO" sz="900"/>
-                <a:t>, 	si </a:t>
+                <a:t>, </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="900" baseline="0"/>
+                <a:t>    </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="900"/>
+                <a:t>si </a:t>
               </a:r>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
@@ -994,7 +1035,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CuadroTexto 13">
@@ -1008,8 +1049,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3537239" y="963181"/>
-              <a:ext cx="2781300" cy="291875"/>
+              <a:off x="3433328" y="841953"/>
+              <a:ext cx="3697432" cy="291875"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1117,7 +1158,13 @@
             <a:p>
               <a:r>
                 <a:rPr lang="es-MX" sz="900"/>
-                <a:t>x = c + </a:t>
+                <a:t>x = </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-MX" sz="900" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>c−</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-MX" sz="900" i="0">
@@ -1133,7 +1180,15 @@
               </a:r>
               <a:r>
                 <a:rPr lang="es-CO" sz="900"/>
-                <a:t>, 	si </a:t>
+                <a:t>, </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="900" baseline="0"/>
+                <a:t>    </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-CO" sz="900"/>
+                <a:t>si </a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-MX" sz="900" b="0" i="0">
@@ -1545,15 +1600,15 @@
       </c>
       <c r="B10" s="3">
         <f ca="1">RAND()</f>
-        <v>5.155599720279902E-2</v>
+        <v>0.31512280964222639</v>
       </c>
       <c r="C10" s="3">
-        <f ca="1">IF(B10&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B10*$C$6*($C$7-$C$5)),$C$7+SQRT((1-B10)*($C$6-$C$5)*($C$7-$C$5)))</f>
-        <v>778.08990597322759</v>
+        <f ca="1">IF(B10&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B10*($C$6-$C$5)*($C$7-$C$5)),$C$7-SQRT((1-B10)*($C$6-$C$5)*($C$7-$C$5)))</f>
+        <v>986.15029284334469</v>
       </c>
       <c r="D10" s="5">
         <f ca="1">INT(C10)</f>
-        <v>778</v>
+        <v>986</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
@@ -1565,15 +1620,15 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:B19" ca="1" si="0">RAND()</f>
-        <v>0.87947264552516047</v>
+        <v>0.84587625722976745</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:C19" ca="1" si="1">IF(B11&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B11*$C$6*($C$7-$C$5)),$C$7+SQRT((1-B11)*($C$6-$C$5)*($C$7-$C$5)))</f>
-        <v>2300.6584704546499</v>
+        <f t="shared" ref="C11:C19" ca="1" si="1">IF(B11&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B11*($C$6-$C$5)*($C$7-$C$5)),$C$7-SQRT((1-B11)*($C$6-$C$5)*($C$7-$C$5)))</f>
+        <v>1660.0105779914993</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" ref="D11:D19" ca="1" si="2">INT(C11)</f>
-        <v>2300</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
@@ -1582,15 +1637,15 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.79060062688561517</v>
+        <v>0.96050028095840689</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2396.2947512089818</v>
+        <v>1827.8814673511454</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>2396</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
@@ -1599,15 +1654,15 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>9.841297070944599E-2</v>
+        <v>0.76072643358896075</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>884.21277446770159</v>
+        <v>1576.3785005358209</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>884</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
@@ -1616,15 +1671,15 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>5.6514766877426736E-2</v>
+        <v>0.44736531251671274</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>791.15657354100745</v>
+        <v>1356.2018828759551</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>791</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
@@ -1633,15 +1688,15 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.976099518665225E-2</v>
+        <v>0.9183678846727884</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>845.89231384923596</v>
+        <v>1752.5649853084478</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>845</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
@@ -1650,15 +1705,15 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47026460322999453</v>
+        <v>0.64667135426079558</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2630.3186079892484</v>
+        <v>1485.2219077074051</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>2630</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
@@ -1667,15 +1722,15 @@
       </c>
       <c r="B17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.52937581586754179</v>
+        <v>0.41834296155110351</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2594.1112169445578</v>
+        <v>1339.5132258427332</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>2594</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
@@ -1684,15 +1739,15 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>7.6012444502412069E-2</v>
+        <v>0.98487482459731401</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>837.66650226757474</v>
+        <v>1893.4923404068304</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>837</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
@@ -1701,15 +1756,15 @@
       </c>
       <c r="B19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.28179289317249623</v>
+        <v>0.55011665120754327</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1150.1456296544216</v>
+        <v>1419.1278009799896</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1150</v>
+        <v>1419</v>
       </c>
     </row>
   </sheetData>

--- a/_downloads/109b9f5d55724f74347a38b45829e0da/Ejemplo distribución triangular.xlsx
+++ b/_downloads/109b9f5d55724f74347a38b45829e0da/Ejemplo distribución triangular.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\migue\Dropbox\ITM\ANÁLISIS DE RIESGOS\Archivos de Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9902A52C-208A-463F-BF0A-6897A5F9E3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5781C5-E538-40A5-B18F-45E6E78188EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{104F5D76-1E87-47BA-AC26-E17CBF973BB8}"/>
   </bookViews>
@@ -69,7 +69,7 @@
     <t>Aleatorio</t>
   </si>
   <si>
-    <t>&gt;=SI(B10&lt;=($C$6-$C$5)/($C$7-$C$5);$C$5+RAIZ(B10*($C$6-$C$5)*($C$7-$C$5));$C$7-RAIZ((1-B10)*($C$6-$C$5)*($C$7-$C$5)))</t>
+    <t>&gt;=SI(B10&lt;=($C$6-$C$5)/($C$7-$C$5);$C$5+RAIZ(B10*($C$6-$C$5)*($C$7-$C$5));$C$7-RAIZ((1-B10)*($C$7-$C$6)*($C$7-$C$5)))</t>
   </si>
 </sst>
 </file>
@@ -193,8 +193,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>6125</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CuadroTexto 12">
@@ -512,7 +512,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CuadroTexto 12">
@@ -886,19 +886,19 @@
                         <a:rPr lang="es-MX" sz="900" b="0" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
+                        <m:t>𝑐</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>−</m:t>
+                      </m:r>
+                      <m:r>
+                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
                         <m:t>𝑏</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                        <m:t>−</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="es-MX" sz="900" b="0" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑎</m:t>
                       </m:r>
                       <m:r>
                         <a:rPr lang="es-MX" sz="900" b="0" i="1">
@@ -1176,7 +1176,7 @@
                 <a:rPr lang="es-MX" sz="900" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>[1−𝑃(&lt;𝑥)](𝑏−𝑎)(𝑐−𝑎))</a:t>
+                <a:t>[1−𝑃(&lt;𝑥)](𝑐−𝑏)(𝑐−𝑎))</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="es-CO" sz="900"/>
@@ -1600,15 +1600,15 @@
       </c>
       <c r="B10" s="3">
         <f ca="1">RAND()</f>
-        <v>0.31512280964222639</v>
+        <v>0.44349385975895195</v>
       </c>
       <c r="C10" s="3">
-        <f ca="1">IF(B10&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B10*($C$6-$C$5)*($C$7-$C$5)),$C$7-SQRT((1-B10)*($C$6-$C$5)*($C$7-$C$5)))</f>
-        <v>986.15029284334469</v>
+        <f ca="1">IF(B10&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B10*($C$6-$C$5)*($C$7-$C$5)),$C$7-SQRT((1-B10)*($C$7-$C$6)*($C$7-$C$5)))</f>
+        <v>1086.3484196031991</v>
       </c>
       <c r="D10" s="5">
         <f ca="1">INT(C10)</f>
-        <v>986</v>
+        <v>1086</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
@@ -1620,15 +1620,15 @@
       </c>
       <c r="B11" s="3">
         <f t="shared" ref="B11:B19" ca="1" si="0">RAND()</f>
-        <v>0.84587625722976745</v>
+        <v>0.52912812704629286</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:C19" ca="1" si="1">IF(B11&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B11*($C$6-$C$5)*($C$7-$C$5)),$C$7-SQRT((1-B11)*($C$6-$C$5)*($C$7-$C$5)))</f>
-        <v>1660.0105779914993</v>
+        <f t="shared" ref="C11:C19" ca="1" si="1">IF(B11&lt;=($C$6-$C$5)/($C$7-$C$5),$C$5+SQRT(B11*($C$6-$C$5)*($C$7-$C$5)),$C$7-SQRT((1-B11)*($C$7-$C$6)*($C$7-$C$5)))</f>
+        <v>1159.578790468398</v>
       </c>
       <c r="D11" s="5">
         <f t="shared" ref="D11:D19" ca="1" si="2">INT(C11)</f>
-        <v>1660</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
@@ -1637,15 +1637,15 @@
       </c>
       <c r="B12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.96050028095840689</v>
+        <v>0.8768832941768766</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1827.8814673511454</v>
+        <v>1570.261639209757</v>
       </c>
       <c r="D12" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1827</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
@@ -1654,15 +1654,15 @@
       </c>
       <c r="B13" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.76072643358896075</v>
+        <v>9.370453905864784E-2</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1576.3785005358209</v>
+        <v>765.10074366924334</v>
       </c>
       <c r="D13" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1576</v>
+        <v>765</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
@@ -1671,15 +1671,15 @@
       </c>
       <c r="B14" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.44736531251671274</v>
+        <v>0.37047193401303413</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1356.2018828759551</v>
+        <v>1028.2530684481435</v>
       </c>
       <c r="D14" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1356</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
@@ -1688,15 +1688,15 @@
       </c>
       <c r="B15" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9183678846727884</v>
+        <v>0.92707467074691496</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1752.5649853084478</v>
+        <v>1669.2614418008877</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1752</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
@@ -1705,15 +1705,15 @@
       </c>
       <c r="B16" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.64667135426079558</v>
+        <v>0.29737669341538608</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1485.2219077074051</v>
+        <v>972.26318939923692</v>
       </c>
       <c r="D16" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1485</v>
+        <v>972</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
@@ -1722,15 +1722,15 @@
       </c>
       <c r="B17" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.41834296155110351</v>
+        <v>0.19922008568715788</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1339.5132258427332</v>
+        <v>886.54244820636245</v>
       </c>
       <c r="D17" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1339</v>
+        <v>886</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
@@ -1739,15 +1739,15 @@
       </c>
       <c r="B18" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.98487482459731401</v>
+        <v>0.57190594387026261</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1893.4923404068304</v>
+        <v>1198.6629397097586</v>
       </c>
       <c r="D18" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1893</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
@@ -1756,15 +1756,15 @@
       </c>
       <c r="B19" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.55011665120754327</v>
+        <v>0.34328298716407724</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1419.1278009799896</v>
+        <v>1007.4902926147854</v>
       </c>
       <c r="D19" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1419</v>
+        <v>1007</v>
       </c>
     </row>
   </sheetData>
